--- a/test/fixtures/real_data/orderkuota_september_anonim.xlsx
+++ b/test/fixtures/real_data/orderkuota_september_anonim.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DONA\Konter\strusa\test\fixtures\real_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4EC707B-88EE-48D1-8412-F9B1452BA8EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DC4C26-0C8A-40AC-9DF2-682A73478A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -355,7 +355,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -363,14 +363,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -503,10 +520,10 @@
   <cols>
     <col min="1" max="1" width="11.26953125" customWidth="1"/>
     <col min="2" max="2" width="19.08984375" customWidth="1"/>
-    <col min="3" max="3" width="27" customWidth="1"/>
-    <col min="4" max="4" width="36.90625" customWidth="1"/>
+    <col min="3" max="3" width="24.6328125" customWidth="1"/>
+    <col min="4" max="4" width="29.90625" customWidth="1"/>
     <col min="5" max="5" width="7.54296875" customWidth="1"/>
-    <col min="6" max="6" width="14.81640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.81640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="7.453125" customWidth="1"/>
     <col min="8" max="8" width="11.7265625" customWidth="1"/>
     <col min="9" max="9" width="15.453125" customWidth="1"/>
@@ -514,817 +531,844 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="2">
         <v>1357810234</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="2">
+      <c r="E2" s="2"/>
+      <c r="F2" s="3">
         <v>87856612234</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>22999</v>
       </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="H2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="A3" s="2">
         <v>1358252698</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="2">
+      <c r="E3" s="2"/>
+      <c r="F3" s="3">
         <v>83845256643</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <v>12200</v>
       </c>
-      <c r="H3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="H3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="A4" s="2">
         <v>1360405559</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="2">
+      <c r="E4" s="2"/>
+      <c r="F4" s="3">
         <v>81370604637</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>0</v>
       </c>
-      <c r="H4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="1" t="s">
+      <c r="H4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" s="2">
         <v>1361100523</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="2">
+      <c r="E5" s="2"/>
+      <c r="F5" s="3">
         <v>81298345671</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="2">
         <v>11200</v>
       </c>
-      <c r="H5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="1" t="s">
+      <c r="H5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="A6" s="2">
         <v>1362462083</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="2">
+      <c r="E6" s="2"/>
+      <c r="F6" s="3">
         <v>83149662211</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="2">
         <v>10000</v>
       </c>
-      <c r="H6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="1" t="s">
+      <c r="H6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="A7" s="2">
         <v>1362990147</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="2">
+      <c r="E7" s="2"/>
+      <c r="F7" s="3">
         <v>85711980022</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="2">
         <v>21500</v>
       </c>
-      <c r="H7" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="1" t="s">
+      <c r="H7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="A8" s="2">
         <v>1363512890</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="2">
+      <c r="E8" s="2"/>
+      <c r="F8" s="3">
         <v>89633120087</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="2">
         <v>9055</v>
       </c>
-      <c r="H8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="1" t="s">
+      <c r="H8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="A9" s="2">
         <v>1364087233</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="2">
+      <c r="E9" s="2"/>
+      <c r="F9" s="3">
         <v>83845217765</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="2">
         <v>33500</v>
       </c>
-      <c r="H9" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="1" t="s">
+      <c r="H9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="A10" s="2">
         <v>1364655781</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="2">
+      <c r="E10" s="2"/>
+      <c r="F10" s="3">
         <v>81345662290</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="2">
         <v>51300</v>
       </c>
-      <c r="H10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="1" t="s">
+      <c r="H10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="A11" s="2">
         <v>1365203456</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="2">
+      <c r="E11" s="2"/>
+      <c r="F11" s="3">
         <v>87712349087</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="2">
         <v>62500</v>
       </c>
-      <c r="H11" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="1" t="s">
+      <c r="H11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="A12" s="2">
         <v>1365789012</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="2">
+      <c r="E12" s="2"/>
+      <c r="F12" s="3">
         <v>85299887766</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="2">
         <v>26400</v>
       </c>
-      <c r="H12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="1" t="s">
+      <c r="H12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="A13" s="2">
         <v>1366345678</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F13" s="2">
+      <c r="E13" s="2"/>
+      <c r="F13" s="3">
         <v>81234509988</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="2">
         <v>202500</v>
       </c>
-      <c r="H13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="1" t="s">
+      <c r="H13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="A14" s="2">
         <v>1366912345</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="2">
+      <c r="E14" s="2"/>
+      <c r="F14" s="3">
         <v>88223311567</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="2">
         <v>45000</v>
       </c>
-      <c r="H14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="1" t="s">
+      <c r="H14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="A15" s="2">
         <v>1367488901</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="2">
+      <c r="E15" s="2"/>
+      <c r="F15" s="3">
         <v>81276543210</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="2">
         <v>0</v>
       </c>
-      <c r="H15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" s="1" t="s">
+      <c r="H15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="A16" s="2">
         <v>1368054567</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="2">
+      <c r="E16" s="2"/>
+      <c r="F16" s="3">
         <v>85711002233</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="2">
         <v>23500</v>
       </c>
-      <c r="H16" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" s="1" t="s">
+      <c r="H16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="A17" s="2">
         <v>1368621234</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="2">
+      <c r="E17" s="2"/>
+      <c r="F17" s="3">
         <v>89544332211</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="2">
         <v>21100</v>
       </c>
-      <c r="H17" t="s">
-        <v>13</v>
-      </c>
-      <c r="I17" s="1" t="s">
+      <c r="H17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="A18" s="2">
         <v>1369198765</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F18" s="2">
+      <c r="E18" s="2"/>
+      <c r="F18" s="3">
         <v>83176654321</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="2">
         <v>31900</v>
       </c>
-      <c r="H18" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" s="1" t="s">
+      <c r="H18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="A19" s="2">
         <v>1369754321</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F19" s="2">
+      <c r="E19" s="2"/>
+      <c r="F19" s="3">
         <v>81345998877</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="2">
         <v>51500</v>
       </c>
-      <c r="H19" t="s">
-        <v>13</v>
-      </c>
-      <c r="I19" s="1" t="s">
+      <c r="H19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="A20" s="2">
         <v>1370331098</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="2">
+      <c r="E20" s="2"/>
+      <c r="F20" s="3">
         <v>87822113344</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="2">
         <v>44900</v>
       </c>
-      <c r="H20" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="1" t="s">
+      <c r="H20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="A21" s="2">
         <v>1370907654</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F21" s="2">
+      <c r="E21" s="2"/>
+      <c r="F21" s="3">
         <v>88113322556</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="2">
         <v>26200</v>
       </c>
-      <c r="H21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="1" t="s">
+      <c r="H21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="A22" s="2">
         <v>1371483210</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F22" s="2">
+      <c r="E22" s="2"/>
+      <c r="F22" s="3">
         <v>89655221144</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="2">
         <v>48900</v>
       </c>
-      <c r="H22" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="1" t="s">
+      <c r="H22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23">
+      <c r="A23" s="2">
         <v>1372059876</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F23" s="2">
+      <c r="E23" s="2"/>
+      <c r="F23" s="3">
         <v>85712233445</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="2">
         <v>51500</v>
       </c>
-      <c r="H23" t="s">
-        <v>13</v>
-      </c>
-      <c r="I23" s="1" t="s">
+      <c r="H23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24">
+      <c r="A24" s="2">
         <v>1372636543</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F24" s="2">
+      <c r="E24" s="2"/>
+      <c r="F24" s="3">
         <v>83145566778</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="2">
         <v>38900</v>
       </c>
-      <c r="H24" t="s">
-        <v>13</v>
-      </c>
-      <c r="I24" s="1" t="s">
+      <c r="H24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25">
+      <c r="A25" s="2">
         <v>1373213109</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F25" s="2">
+      <c r="E25" s="2"/>
+      <c r="F25" s="3">
         <v>81334455667</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="2">
         <v>102500</v>
       </c>
-      <c r="H25" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" s="1" t="s">
+      <c r="H25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J25" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26">
+      <c r="A26" s="2">
         <v>1373789765</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F26" s="2">
+      <c r="E26" s="2"/>
+      <c r="F26" s="3">
         <v>83172233445</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="2">
         <v>55000</v>
       </c>
-      <c r="H26" t="s">
-        <v>13</v>
-      </c>
-      <c r="I26" s="1" t="s">
+      <c r="H26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27">
+      <c r="A27" s="2">
         <v>1374366321</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F27" s="2">
+      <c r="E27" s="2"/>
+      <c r="F27" s="3">
         <v>85611223399</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="2">
         <v>16100</v>
       </c>
-      <c r="H27" t="s">
-        <v>13</v>
-      </c>
-      <c r="I27" s="1" t="s">
+      <c r="H27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28">
+      <c r="A28" s="2">
         <v>1374942987</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F28" s="2">
+      <c r="E28" s="2"/>
+      <c r="F28" s="3">
         <v>87728156600</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="2">
         <v>76500</v>
       </c>
-      <c r="H28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I28" s="1" t="s">
+      <c r="H28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" s="2" t="s">
         <v>15</v>
       </c>
     </row>
